--- a/assets/donnees_test_import.xlsx
+++ b/assets/donnees_test_import.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\dashboard2\assets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE44BC0-4B8B-446D-9960-E649EA98B359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Financier" sheetId="1" r:id="rId1"/>
@@ -21,12 +15,12 @@
     <sheet name="KPI Hebdo" sheetId="6" r:id="rId6"/>
     <sheet name="Bénéficiaires" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="133">
   <si>
     <t>date</t>
   </si>
@@ -130,9 +124,6 @@
     <t>transactions</t>
   </si>
   <si>
-    <t>score_discipline</t>
-  </si>
-  <si>
     <t>Nom</t>
   </si>
   <si>
@@ -425,16 +416,21 @@
   </si>
   <si>
     <t>Taux digitalisation (%)</t>
+  </si>
+  <si>
+    <t>Score discipline (%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,29 +500,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -564,7 +552,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -598,7 +586,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -633,10 +620,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -809,29 +795,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -875,42 +843,42 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2">
-        <v>581177.58025645709</v>
+        <v>493645.3793139897</v>
       </c>
       <c r="C2">
-        <v>396519.35744877311</v>
+        <v>434327.8621197357</v>
       </c>
       <c r="D2">
         <v>10000000</v>
       </c>
       <c r="E2">
-        <v>213211.32044048939</v>
+        <v>226839.9436015147</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>489706.15781652043</v>
+        <v>424385.9941841833</v>
       </c>
       <c r="I2">
         <v>50</v>
       </c>
       <c r="J2">
-        <v>10171.439227912701</v>
+        <v>11505.38171424083</v>
       </c>
       <c r="K2">
         <v>10000000</v>
@@ -922,47 +890,47 @@
         <v>50</v>
       </c>
       <c r="N2">
-        <v>5540.3117893331373</v>
+        <v>5271.885168480726</v>
       </c>
       <c r="O2" s="3">
-        <f t="shared" ref="O2:O31" si="0">IF(B2=0, 0, H2/B2)</f>
-        <v>0.84261020117194996</v>
+        <f>IF(B2=0, 0, H2/B2)</f>
+        <v>0</v>
       </c>
       <c r="P2" s="4">
-        <f t="shared" ref="P2:P31" si="1">IF(I2=0, 0, H2/I2)</f>
-        <v>9794.1231563304082</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I2=0, 0, H2/I2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3">
-        <v>545130.29852134583</v>
+        <v>456381.1463646519</v>
       </c>
       <c r="C3">
-        <v>551410.7282400179</v>
+        <v>453053.7752877968</v>
       </c>
       <c r="D3">
         <v>10000000</v>
       </c>
       <c r="E3">
-        <v>199394.84360803</v>
+        <v>205557.6937116839</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>478114.41245310428</v>
+        <v>511061.2936217328</v>
       </c>
       <c r="I3">
         <v>50</v>
       </c>
       <c r="J3">
-        <v>11872.16430719211</v>
+        <v>11983.45320482067</v>
       </c>
       <c r="K3">
         <v>10000000</v>
@@ -974,47 +942,47 @@
         <v>50</v>
       </c>
       <c r="N3">
-        <v>3208.104481648109</v>
+        <v>5664.159683990094</v>
       </c>
       <c r="O3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.87706446284490025</v>
+        <f>IF(B3=0, 0, H3/B3)</f>
+        <v>0</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" si="1"/>
-        <v>9562.288249062085</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I3=0, 0, H3/I3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4">
-        <v>401798.84072130022</v>
+        <v>394703.9122846924</v>
       </c>
       <c r="C4">
-        <v>524693.35143813933</v>
+        <v>371256.5413761474</v>
       </c>
       <c r="D4">
         <v>10000000</v>
       </c>
       <c r="E4">
-        <v>245860.38197211141</v>
+        <v>185363.3200982215</v>
       </c>
       <c r="F4">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>486119.63847018289</v>
+        <v>486987.0457054129</v>
       </c>
       <c r="I4">
         <v>50</v>
       </c>
       <c r="J4">
-        <v>10874.07603230506</v>
+        <v>7653.311322407956</v>
       </c>
       <c r="K4">
         <v>10000000</v>
@@ -1026,47 +994,47 @@
         <v>50</v>
       </c>
       <c r="N4">
-        <v>4180.9545819004961</v>
+        <v>5591.15244233651</v>
       </c>
       <c r="O4" s="3">
-        <f t="shared" si="0"/>
-        <v>1.2098582405004252</v>
+        <f>IF(B4=0, 0, H4/B4)</f>
+        <v>0</v>
       </c>
       <c r="P4" s="4">
-        <f t="shared" si="1"/>
-        <v>9722.3927694036574</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I4=0, 0, H4/I4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5">
-        <v>464044.85279599781</v>
+        <v>511392.4924307726</v>
       </c>
       <c r="C5">
-        <v>449260.22241666389</v>
+        <v>503408.1000559106</v>
       </c>
       <c r="D5">
         <v>10000000</v>
       </c>
       <c r="E5">
-        <v>208679.38681439069</v>
+        <v>183962.8694743191</v>
       </c>
       <c r="F5">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5">
-        <v>533034.25022739707</v>
+        <v>458863.6778290983</v>
       </c>
       <c r="I5">
         <v>50</v>
       </c>
       <c r="J5">
-        <v>8945.2408776493849</v>
+        <v>9756.349573260379</v>
       </c>
       <c r="K5">
         <v>10000000</v>
@@ -1078,47 +1046,47 @@
         <v>50</v>
       </c>
       <c r="N5">
-        <v>4979.1851021520979</v>
+        <v>4100.33051376091</v>
       </c>
       <c r="O5" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1486696749586149</v>
+        <f>IF(B5=0, 0, H5/B5)</f>
+        <v>0</v>
       </c>
       <c r="P5" s="4">
-        <f t="shared" si="1"/>
-        <v>10660.685004547942</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I5=0, 0, H5/I5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6">
-        <v>473857.33858826919</v>
+        <v>499389.9835166802</v>
       </c>
       <c r="C6">
-        <v>432658.01556861523</v>
+        <v>598666.1715810976</v>
       </c>
       <c r="D6">
         <v>10000000</v>
       </c>
       <c r="E6">
-        <v>188196.001709537</v>
+        <v>215943.248466615</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>50</v>
       </c>
       <c r="H6">
-        <v>484814.26294720091</v>
+        <v>468129.0099426164</v>
       </c>
       <c r="I6">
         <v>50</v>
       </c>
       <c r="J6">
-        <v>10352.392255012121</v>
+        <v>11646.83356624163</v>
       </c>
       <c r="K6">
         <v>10000000</v>
@@ -1130,47 +1098,47 @@
         <v>50</v>
       </c>
       <c r="N6">
-        <v>5150.4858465048974</v>
+        <v>3670.603650412196</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0231228335337696</v>
+        <f>IF(B6=0, 0, H6/B6)</f>
+        <v>0</v>
       </c>
       <c r="P6" s="4">
-        <f t="shared" si="1"/>
-        <v>9696.285258944019</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I6=0, 0, H6/I6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7">
-        <v>464976.06952492392</v>
+        <v>449696.2245809882</v>
       </c>
       <c r="C7">
-        <v>529409.11917820363</v>
+        <v>536768.3358024193</v>
       </c>
       <c r="D7">
         <v>10000000</v>
       </c>
       <c r="E7">
-        <v>192881.52699429731</v>
+        <v>204206.6784134559</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="H7">
-        <v>541890.06756369094</v>
+        <v>535415.31707789</v>
       </c>
       <c r="I7">
         <v>50</v>
       </c>
       <c r="J7">
-        <v>12899.125407879499</v>
+        <v>10441.99806979415</v>
       </c>
       <c r="K7">
         <v>10000000</v>
@@ -1182,47 +1150,47 @@
         <v>50</v>
       </c>
       <c r="N7">
-        <v>4407.3240211613629</v>
+        <v>6045.977306467833</v>
       </c>
       <c r="O7" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1654149602093538</v>
+        <f>IF(B7=0, 0, H7/B7)</f>
+        <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f t="shared" si="1"/>
-        <v>10837.801351273818</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I7=0, 0, H7/I7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8">
-        <v>576987.35823018663</v>
+        <v>451594.7327288359</v>
       </c>
       <c r="C8">
-        <v>414032.25061753078</v>
+        <v>416864.4334411807</v>
       </c>
       <c r="D8">
         <v>10000000</v>
       </c>
       <c r="E8">
-        <v>208304.53891810431</v>
+        <v>191876.3008110393</v>
       </c>
       <c r="F8">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>50</v>
       </c>
       <c r="H8">
-        <v>377605.79498167918</v>
+        <v>483914.0607879292</v>
       </c>
       <c r="I8">
         <v>50</v>
       </c>
       <c r="J8">
-        <v>11493.069577265291</v>
+        <v>10065.3702987974</v>
       </c>
       <c r="K8">
         <v>10000000</v>
@@ -1234,47 +1202,47 @@
         <v>50</v>
       </c>
       <c r="N8">
-        <v>4395.7603619205474</v>
+        <v>5716.343041561295</v>
       </c>
       <c r="O8" s="3">
-        <f t="shared" si="0"/>
-        <v>0.65444379256405649</v>
+        <f>IF(B8=0, 0, H8/B8)</f>
+        <v>0</v>
       </c>
       <c r="P8" s="4">
-        <f t="shared" si="1"/>
-        <v>7552.1158996335835</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I8=0, 0, H8/I8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
       <c r="B9">
-        <v>525617.23732861644</v>
+        <v>491115.7432744828</v>
       </c>
       <c r="C9">
-        <v>479313.27981462411</v>
+        <v>498634.4954101164</v>
       </c>
       <c r="D9">
         <v>10000000</v>
       </c>
       <c r="E9">
-        <v>218843.10274637429</v>
+        <v>205271.183545514</v>
       </c>
       <c r="F9">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9">
         <v>50</v>
       </c>
       <c r="H9">
-        <v>424979.69516245718</v>
+        <v>415086.9162565423</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9">
-        <v>8986.2931407753549</v>
+        <v>8297.910423895613</v>
       </c>
       <c r="K9">
         <v>10000000</v>
@@ -1286,47 +1254,47 @@
         <v>50</v>
       </c>
       <c r="N9">
-        <v>4296.2952185657614</v>
+        <v>3922.656978228487</v>
       </c>
       <c r="O9" s="3">
-        <f t="shared" si="0"/>
-        <v>0.80853454753950438</v>
+        <f>IF(B9=0, 0, H9/B9)</f>
+        <v>0</v>
       </c>
       <c r="P9" s="4">
-        <f t="shared" si="1"/>
-        <v>8499.5939032491442</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I9=0, 0, H9/I9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10">
-        <v>478665.08213538659</v>
+        <v>451221.1869599861</v>
       </c>
       <c r="C10">
-        <v>521726.29281465907</v>
+        <v>402942.3022238618</v>
       </c>
       <c r="D10">
         <v>10000000</v>
       </c>
       <c r="E10">
-        <v>196406.40094471569</v>
+        <v>185045.3837073969</v>
       </c>
       <c r="F10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>50</v>
       </c>
       <c r="H10">
-        <v>355194.70206359727</v>
+        <v>558812.6181181637</v>
       </c>
       <c r="I10">
         <v>50</v>
       </c>
       <c r="J10">
-        <v>10816.848261575051</v>
+        <v>8890.60410013125</v>
       </c>
       <c r="K10">
         <v>10000000</v>
@@ -1338,47 +1306,47 @@
         <v>50</v>
       </c>
       <c r="N10">
-        <v>5243.6560149311053</v>
+        <v>3852.200372208685</v>
       </c>
       <c r="O10" s="3">
-        <f t="shared" si="0"/>
-        <v>0.74205266964330874</v>
+        <f>IF(B10=0, 0, H10/B10)</f>
+        <v>0</v>
       </c>
       <c r="P10" s="4">
-        <f t="shared" si="1"/>
-        <v>7103.8940412719458</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I10=0, 0, H10/I10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
       <c r="B11">
-        <v>516019.41171962739</v>
+        <v>420689.5623026744</v>
       </c>
       <c r="C11">
-        <v>571842.77840115037</v>
+        <v>522402.7436656601</v>
       </c>
       <c r="D11">
         <v>10000000</v>
       </c>
       <c r="E11">
-        <v>227195.34231000909</v>
+        <v>233186.0175224457</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G11">
         <v>50</v>
       </c>
       <c r="H11">
-        <v>505832.05276445037</v>
+        <v>466803.4231665413</v>
       </c>
       <c r="I11">
         <v>50</v>
       </c>
       <c r="J11">
-        <v>10295.027820333329</v>
+        <v>12355.2609612883</v>
       </c>
       <c r="K11">
         <v>10000000</v>
@@ -1390,47 +1358,47 @@
         <v>50</v>
       </c>
       <c r="N11">
-        <v>5184.796847997889</v>
+        <v>3740.816645561712</v>
       </c>
       <c r="O11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98025779898235266</v>
+        <f>IF(B11=0, 0, H11/B11)</f>
+        <v>0</v>
       </c>
       <c r="P11" s="4">
-        <f t="shared" si="1"/>
-        <v>10116.641055289008</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I11=0, 0, H11/I11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12">
-        <v>519006.7524738193</v>
+        <v>470294.9340446929</v>
       </c>
       <c r="C12">
-        <v>465705.54387034982</v>
+        <v>465835.6067070418</v>
       </c>
       <c r="D12">
         <v>10000000</v>
       </c>
       <c r="E12">
-        <v>168550.701007645</v>
+        <v>214398.1509182421</v>
       </c>
       <c r="F12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>50</v>
       </c>
       <c r="H12">
-        <v>542584.61053700454</v>
+        <v>525887.9981279785</v>
       </c>
       <c r="I12">
         <v>50</v>
       </c>
       <c r="J12">
-        <v>8438.5117474049694</v>
+        <v>8692.416227544782</v>
       </c>
       <c r="K12">
         <v>10000000</v>
@@ -1442,47 +1410,47 @@
         <v>50</v>
       </c>
       <c r="N12">
-        <v>4144.4691629966073</v>
+        <v>4917.368825323164</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0454288079120408</v>
+        <f>IF(B12=0, 0, H12/B12)</f>
+        <v>0</v>
       </c>
       <c r="P12" s="4">
-        <f t="shared" si="1"/>
-        <v>10851.692210740091</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I12=0, 0, H12/I12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13">
-        <v>507995.90129241563</v>
+        <v>454780.3338201803</v>
       </c>
       <c r="C13">
-        <v>442624.95117725508</v>
+        <v>428178.9441229068</v>
       </c>
       <c r="D13">
         <v>10000000</v>
       </c>
       <c r="E13">
-        <v>208548.00870523931</v>
+        <v>204775.9404355896</v>
       </c>
       <c r="F13">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G13">
         <v>50</v>
       </c>
       <c r="H13">
-        <v>468002.06569957838</v>
+        <v>456364.0389130302</v>
       </c>
       <c r="I13">
         <v>50</v>
       </c>
       <c r="J13">
-        <v>11999.64328680757</v>
+        <v>11171.93187347951</v>
       </c>
       <c r="K13">
         <v>10000000</v>
@@ -1494,47 +1462,47 @@
         <v>50</v>
       </c>
       <c r="N13">
-        <v>4900.5159875336694</v>
+        <v>4632.608410580337</v>
       </c>
       <c r="O13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92127134197128935</v>
+        <f>IF(B13=0, 0, H13/B13)</f>
+        <v>0</v>
       </c>
       <c r="P13" s="4">
-        <f t="shared" si="1"/>
-        <v>9360.0413139915672</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I13=0, 0, H13/I13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
       <c r="B14">
-        <v>572490.33034007857</v>
+        <v>537975.7798002912</v>
       </c>
       <c r="C14">
-        <v>458794.99043777602</v>
+        <v>540285.348705261</v>
       </c>
       <c r="D14">
         <v>10000000</v>
       </c>
       <c r="E14">
-        <v>176604.59762771969</v>
+        <v>225821.2033822534</v>
       </c>
       <c r="F14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G14">
         <v>50</v>
       </c>
       <c r="H14">
-        <v>429780.81483698369</v>
+        <v>331113.0171518801</v>
       </c>
       <c r="I14">
         <v>50</v>
       </c>
       <c r="J14">
-        <v>10464.472767590671</v>
+        <v>11111.2652204737</v>
       </c>
       <c r="K14">
         <v>10000000</v>
@@ -1546,47 +1514,47 @@
         <v>50</v>
       </c>
       <c r="N14">
-        <v>4940.9887024801492</v>
+        <v>5257.783527422703</v>
       </c>
       <c r="O14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.7507215267403371</v>
+        <f>IF(B14=0, 0, H14/B14)</f>
+        <v>0</v>
       </c>
       <c r="P14" s="4">
-        <f t="shared" si="1"/>
-        <v>8595.616296739674</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I14=0, 0, H14/I14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15">
-        <v>470697.81711850478</v>
+        <v>515273.3250955886</v>
       </c>
       <c r="C15">
-        <v>509188.04003980441</v>
+        <v>536523.0993997363</v>
       </c>
       <c r="D15">
         <v>10000000</v>
       </c>
       <c r="E15">
-        <v>201000.89643215109</v>
+        <v>234306.9440459144</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G15">
         <v>50</v>
       </c>
       <c r="H15">
-        <v>473135.95890016621</v>
+        <v>460458.0049379909</v>
       </c>
       <c r="I15">
         <v>50</v>
       </c>
       <c r="J15">
-        <v>12284.69530400142</v>
+        <v>12735.81644410109</v>
       </c>
       <c r="K15">
         <v>10000000</v>
@@ -1598,47 +1566,47 @@
         <v>50</v>
       </c>
       <c r="N15">
-        <v>5747.3277515733362</v>
+        <v>3729.25279309255</v>
       </c>
       <c r="O15" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0051798451001688</v>
+        <f>IF(B15=0, 0, H15/B15)</f>
+        <v>0</v>
       </c>
       <c r="P15" s="4">
-        <f t="shared" si="1"/>
-        <v>9462.7191780033245</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I15=0, 0, H15/I15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16">
-        <v>492772.58733912569</v>
+        <v>529650.8967078481</v>
       </c>
       <c r="C16">
-        <v>585769.98922302807</v>
+        <v>427564.9777221395</v>
       </c>
       <c r="D16">
         <v>10000000</v>
       </c>
       <c r="E16">
-        <v>200068.6989246367</v>
+        <v>204519.2696056191</v>
       </c>
       <c r="F16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G16">
         <v>50</v>
       </c>
       <c r="H16">
-        <v>543516.81210219918</v>
+        <v>503027.5770098641</v>
       </c>
       <c r="I16">
         <v>50</v>
       </c>
       <c r="J16">
-        <v>11042.70897062004</v>
+        <v>8379.055450397065</v>
       </c>
       <c r="K16">
         <v>10000000</v>
@@ -1650,47 +1618,47 @@
         <v>50</v>
       </c>
       <c r="N16">
-        <v>5717.6682304888755</v>
+        <v>4316.877990084983</v>
       </c>
       <c r="O16" s="3">
-        <f t="shared" si="0"/>
-        <v>1.102976963546374</v>
+        <f>IF(B16=0, 0, H16/B16)</f>
+        <v>0</v>
       </c>
       <c r="P16" s="4">
-        <f t="shared" si="1"/>
-        <v>10870.336242043984</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I16=0, 0, H16/I16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17">
-        <v>531387.62123046617</v>
+        <v>450381.6432234772</v>
       </c>
       <c r="C17">
-        <v>526610.27083025069</v>
+        <v>389899.8563856973</v>
       </c>
       <c r="D17">
         <v>10000000</v>
       </c>
       <c r="E17">
-        <v>171643.0963966432</v>
+        <v>210004.6149862976</v>
       </c>
       <c r="F17">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G17">
         <v>50</v>
       </c>
       <c r="H17">
-        <v>524542.17463610903</v>
+        <v>404362.8112500649</v>
       </c>
       <c r="I17">
         <v>50</v>
       </c>
       <c r="J17">
-        <v>12201.947366372469</v>
+        <v>14634.36773517672</v>
       </c>
       <c r="K17">
         <v>10000000</v>
@@ -1702,47 +1670,47 @@
         <v>50</v>
       </c>
       <c r="N17">
-        <v>3778.984588463547</v>
+        <v>5879.573184700711</v>
       </c>
       <c r="O17" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98711779062804283</v>
+        <f>IF(B17=0, 0, H17/B17)</f>
+        <v>0</v>
       </c>
       <c r="P17" s="4">
-        <f t="shared" si="1"/>
-        <v>10490.843492722181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I17=0, 0, H17/I17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18">
-        <v>523564.37978617247</v>
+        <v>495020.6350733085</v>
       </c>
       <c r="C18">
-        <v>563547.87972245808</v>
+        <v>455247.3189553149</v>
       </c>
       <c r="D18">
         <v>10000000</v>
       </c>
       <c r="E18">
-        <v>198331.4413005219</v>
+        <v>222167.9190344207</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G18">
         <v>50</v>
       </c>
       <c r="H18">
-        <v>471071.46799849521</v>
+        <v>483428.2772121969</v>
       </c>
       <c r="I18">
         <v>50</v>
       </c>
       <c r="J18">
-        <v>9159.8602073065231</v>
+        <v>12695.42890054143</v>
       </c>
       <c r="K18">
         <v>10000000</v>
@@ -1754,47 +1722,47 @@
         <v>50</v>
       </c>
       <c r="N18">
-        <v>4999.0593746531222</v>
+        <v>4867.498556305623</v>
       </c>
       <c r="O18" s="3">
-        <f t="shared" si="0"/>
-        <v>0.89973933710097742</v>
+        <f>IF(B18=0, 0, H18/B18)</f>
+        <v>0</v>
       </c>
       <c r="P18" s="4">
-        <f t="shared" si="1"/>
-        <v>9421.4293599699049</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I18=0, 0, H18/I18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19">
-        <v>548637.01768663456</v>
+        <v>573020.0642683784</v>
       </c>
       <c r="C19">
-        <v>390443.69078843779</v>
+        <v>516922.54960293</v>
       </c>
       <c r="D19">
         <v>10000000</v>
       </c>
       <c r="E19">
-        <v>218074.70123680591</v>
+        <v>203354.4882150041</v>
       </c>
       <c r="F19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19">
         <v>50</v>
       </c>
       <c r="H19">
-        <v>580012.40303006291</v>
+        <v>461025.1969709177</v>
       </c>
       <c r="I19">
         <v>50</v>
       </c>
       <c r="J19">
-        <v>14201.566784531569</v>
+        <v>12417.58031981815</v>
       </c>
       <c r="K19">
         <v>10000000</v>
@@ -1806,47 +1774,47 @@
         <v>50</v>
       </c>
       <c r="N19">
-        <v>4392.6560732783437</v>
+        <v>3994.504288610516</v>
       </c>
       <c r="O19" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0571878752835979</v>
+        <f>IF(B19=0, 0, H19/B19)</f>
+        <v>0</v>
       </c>
       <c r="P19" s="4">
-        <f t="shared" si="1"/>
-        <v>11600.248060601258</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I19=0, 0, H19/I19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20">
-        <v>540686.39812826086</v>
+        <v>490162.2550219741</v>
       </c>
       <c r="C20">
-        <v>556156.02314509056</v>
+        <v>511658.9493570831</v>
       </c>
       <c r="D20">
         <v>10000000</v>
       </c>
       <c r="E20">
-        <v>201627.9350413389</v>
+        <v>209221.2025428882</v>
       </c>
       <c r="F20">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G20">
         <v>50</v>
       </c>
       <c r="H20">
-        <v>405105.3645159048</v>
+        <v>407058.2995163593</v>
       </c>
       <c r="I20">
         <v>50</v>
       </c>
       <c r="J20">
-        <v>8262.5398036806255</v>
+        <v>6417.803716449853</v>
       </c>
       <c r="K20">
         <v>10000000</v>
@@ -1858,32 +1826,32 @@
         <v>50</v>
       </c>
       <c r="N20">
-        <v>5386.6165484501762</v>
+        <v>4122.940173710485</v>
       </c>
       <c r="O20" s="3">
-        <f t="shared" si="0"/>
-        <v>0.74924275128483309</v>
+        <f>IF(B20=0, 0, H20/B20)</f>
+        <v>0</v>
       </c>
       <c r="P20" s="4">
-        <f t="shared" si="1"/>
-        <v>8102.1072903180957</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I20=0, 0, H20/I20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21">
-        <v>543430.85738071112</v>
+        <v>495868.4858266176</v>
       </c>
       <c r="C21">
-        <v>523055.22863609379</v>
+        <v>479497.5851648818</v>
       </c>
       <c r="D21">
         <v>10000000</v>
       </c>
       <c r="E21">
-        <v>196035.2723436408</v>
+        <v>172728.3524920741</v>
       </c>
       <c r="F21">
         <v>42</v>
@@ -1892,13 +1860,13 @@
         <v>50</v>
       </c>
       <c r="H21">
-        <v>565463.74068395724</v>
+        <v>435313.4921819763</v>
       </c>
       <c r="I21">
         <v>50</v>
       </c>
       <c r="J21">
-        <v>11387.78680325829</v>
+        <v>10660.59748545865</v>
       </c>
       <c r="K21">
         <v>10000000</v>
@@ -1910,47 +1878,47 @@
         <v>50</v>
       </c>
       <c r="N21">
-        <v>3348.9164536895678</v>
+        <v>5158.888917583404</v>
       </c>
       <c r="O21" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0405440416273795</v>
+        <f>IF(B21=0, 0, H21/B21)</f>
+        <v>0</v>
       </c>
       <c r="P21" s="4">
-        <f t="shared" si="1"/>
-        <v>11309.274813679145</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I21=0, 0, H21/I21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
       <c r="B22">
-        <v>367302.93616274261</v>
+        <v>455288.7099512532</v>
       </c>
       <c r="C22">
-        <v>439339.79561049532</v>
+        <v>366179.7685466458</v>
       </c>
       <c r="D22">
         <v>10000000</v>
       </c>
       <c r="E22">
-        <v>195007.31580635969</v>
+        <v>246695.5669517631</v>
       </c>
       <c r="F22">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G22">
         <v>50</v>
       </c>
       <c r="H22">
-        <v>530501.3302710274</v>
+        <v>489622.7181050243</v>
       </c>
       <c r="I22">
         <v>50</v>
       </c>
       <c r="J22">
-        <v>9716.789539511672</v>
+        <v>9319.897720194971</v>
       </c>
       <c r="K22">
         <v>10000000</v>
@@ -1962,47 +1930,47 @@
         <v>50</v>
       </c>
       <c r="N22">
-        <v>3386.739090412314</v>
+        <v>4177.424825145677</v>
       </c>
       <c r="O22" s="3">
-        <f t="shared" si="0"/>
-        <v>1.4443155173580635</v>
+        <f>IF(B22=0, 0, H22/B22)</f>
+        <v>0</v>
       </c>
       <c r="P22" s="4">
-        <f t="shared" si="1"/>
-        <v>10610.026605420548</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I22=0, 0, H22/I22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
       <c r="B23">
-        <v>497535.87906622229</v>
+        <v>418322.494106073</v>
       </c>
       <c r="C23">
-        <v>564196.50750729733</v>
+        <v>532658.4046197992</v>
       </c>
       <c r="D23">
         <v>10000000</v>
       </c>
       <c r="E23">
-        <v>204024.1747683885</v>
+        <v>201786.331774403</v>
       </c>
       <c r="F23">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G23">
         <v>50</v>
       </c>
       <c r="H23">
-        <v>475064.38004266162</v>
+        <v>594158.4500419693</v>
       </c>
       <c r="I23">
         <v>50</v>
       </c>
       <c r="J23">
-        <v>9374.4998554576196</v>
+        <v>11322.70529301259</v>
       </c>
       <c r="K23">
         <v>10000000</v>
@@ -2014,47 +1982,47 @@
         <v>50</v>
       </c>
       <c r="N23">
-        <v>4759.0054619878747</v>
+        <v>5368.687830403747</v>
       </c>
       <c r="O23" s="3">
-        <f t="shared" si="0"/>
-        <v>0.95483441502603739</v>
+        <f>IF(B23=0, 0, H23/B23)</f>
+        <v>0</v>
       </c>
       <c r="P23" s="4">
-        <f t="shared" si="1"/>
-        <v>9501.287600853233</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I23=0, 0, H23/I23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
       <c r="B24">
-        <v>514581.10563964478</v>
+        <v>565144.4273422362</v>
       </c>
       <c r="C24">
-        <v>438618.04180994863</v>
+        <v>447442.7269523522</v>
       </c>
       <c r="D24">
         <v>10000000</v>
       </c>
       <c r="E24">
-        <v>208848.31294656359</v>
+        <v>192409.0514656247</v>
       </c>
       <c r="F24">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G24">
         <v>50</v>
       </c>
       <c r="H24">
-        <v>427587.7507581627</v>
+        <v>475058.536785207</v>
       </c>
       <c r="I24">
         <v>50</v>
       </c>
       <c r="J24">
-        <v>10312.325694071609</v>
+        <v>11831.14644841228</v>
       </c>
       <c r="K24">
         <v>10000000</v>
@@ -2066,47 +2034,47 @@
         <v>50</v>
       </c>
       <c r="N24">
-        <v>3667.9046836380121</v>
+        <v>4929.701474962088</v>
       </c>
       <c r="O24" s="3">
-        <f t="shared" si="0"/>
-        <v>0.83094335581298528</v>
+        <f>IF(B24=0, 0, H24/B24)</f>
+        <v>0</v>
       </c>
       <c r="P24" s="4">
-        <f t="shared" si="1"/>
-        <v>8551.7550151632531</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I24=0, 0, H24/I24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
       <c r="B25">
-        <v>502866.98682670231</v>
+        <v>561718.9679860667</v>
       </c>
       <c r="C25">
-        <v>563129.08243561967</v>
+        <v>455715.8598405081</v>
       </c>
       <c r="D25">
         <v>10000000</v>
       </c>
       <c r="E25">
-        <v>194487.3253097884</v>
+        <v>175662.5174786804</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G25">
         <v>50</v>
       </c>
       <c r="H25">
-        <v>491796.35674546729</v>
+        <v>506869.3177669081</v>
       </c>
       <c r="I25">
         <v>50</v>
       </c>
       <c r="J25">
-        <v>6640.9417491757567</v>
+        <v>8154.233627951305</v>
       </c>
       <c r="K25">
         <v>10000000</v>
@@ -2118,47 +2086,47 @@
         <v>50</v>
       </c>
       <c r="N25">
-        <v>4472.7453043782734</v>
+        <v>6061.934516132404</v>
       </c>
       <c r="O25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.97798497341991919</v>
+        <f>IF(B25=0, 0, H25/B25)</f>
+        <v>0</v>
       </c>
       <c r="P25" s="4">
-        <f t="shared" si="1"/>
-        <v>9835.9271349093451</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I25=0, 0, H25/I25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
       <c r="B26">
-        <v>571667.38510539394</v>
+        <v>434337.5166861727</v>
       </c>
       <c r="C26">
-        <v>520540.91586683219</v>
+        <v>491220.1589657255</v>
       </c>
       <c r="D26">
         <v>10000000</v>
       </c>
       <c r="E26">
-        <v>169592.87022831189</v>
+        <v>238065.605190019</v>
       </c>
       <c r="F26">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G26">
         <v>50</v>
       </c>
       <c r="H26">
-        <v>460861.41815649893</v>
+        <v>480774.1954603907</v>
       </c>
       <c r="I26">
         <v>50</v>
       </c>
       <c r="J26">
-        <v>10094.341475795291</v>
+        <v>5851.510638184146</v>
       </c>
       <c r="K26">
         <v>10000000</v>
@@ -2170,47 +2138,47 @@
         <v>50</v>
       </c>
       <c r="N26">
-        <v>4827.7120067648684</v>
+        <v>4200.520507775738</v>
       </c>
       <c r="O26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.80617056380002061</v>
+        <f>IF(B26=0, 0, H26/B26)</f>
+        <v>0</v>
       </c>
       <c r="P26" s="4">
-        <f t="shared" si="1"/>
-        <v>9217.2283631299779</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I26=0, 0, H26/I26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
       <c r="B27">
-        <v>450674.89980505768</v>
+        <v>547988.0499220025</v>
       </c>
       <c r="C27">
-        <v>424100.01027254888</v>
+        <v>548336.5413437431</v>
       </c>
       <c r="D27">
         <v>10000000</v>
       </c>
       <c r="E27">
-        <v>200357.49836598159</v>
+        <v>168015.1788265475</v>
       </c>
       <c r="F27">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G27">
         <v>50</v>
       </c>
       <c r="H27">
-        <v>499448.9150163962</v>
+        <v>406113.5202012096</v>
       </c>
       <c r="I27">
         <v>50</v>
       </c>
       <c r="J27">
-        <v>13133.548216707661</v>
+        <v>10841.37367649777</v>
       </c>
       <c r="K27">
         <v>10000000</v>
@@ -2222,47 +2190,47 @@
         <v>50</v>
       </c>
       <c r="N27">
-        <v>3544.3942193303578</v>
+        <v>5128.302855022217</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1082243879844118</v>
+        <f>IF(B27=0, 0, H27/B27)</f>
+        <v>0</v>
       </c>
       <c r="P27" s="4">
-        <f t="shared" si="1"/>
-        <v>9988.9783003279244</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I27=0, 0, H27/I27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
       <c r="B28">
-        <v>457941.50560125691</v>
+        <v>522030.7867718767</v>
       </c>
       <c r="C28">
-        <v>494855.7939027914</v>
+        <v>352214.4120675199</v>
       </c>
       <c r="D28">
         <v>10000000</v>
       </c>
       <c r="E28">
-        <v>181074.5595807418</v>
+        <v>226409.1185601307</v>
       </c>
       <c r="F28">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G28">
         <v>50</v>
       </c>
       <c r="H28">
-        <v>512098.15739453287</v>
+        <v>541508.1026363616</v>
       </c>
       <c r="I28">
         <v>50</v>
       </c>
       <c r="J28">
-        <v>8069.8576318269788</v>
+        <v>9942.854251075418</v>
       </c>
       <c r="K28">
         <v>10000000</v>
@@ -2274,47 +2242,47 @@
         <v>50</v>
       </c>
       <c r="N28">
-        <v>3909.937548261852</v>
+        <v>5102.933820323808</v>
       </c>
       <c r="O28" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1182610685663241</v>
+        <f>IF(B28=0, 0, H28/B28)</f>
+        <v>0</v>
       </c>
       <c r="P28" s="4">
-        <f t="shared" si="1"/>
-        <v>10241.963147890658</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I28=0, 0, H28/I28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
       <c r="B29">
-        <v>471051.12945488608</v>
+        <v>499319.0184899765</v>
       </c>
       <c r="C29">
-        <v>421661.95863326109</v>
+        <v>539240.4108657291</v>
       </c>
       <c r="D29">
         <v>10000000</v>
       </c>
       <c r="E29">
-        <v>215794.99958536259</v>
+        <v>212582.8662941818</v>
       </c>
       <c r="F29">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G29">
         <v>50</v>
       </c>
       <c r="H29">
-        <v>559439.72773369343</v>
+        <v>501713.6705925093</v>
       </c>
       <c r="I29">
         <v>50</v>
       </c>
       <c r="J29">
-        <v>9317.8045347823863</v>
+        <v>12893.39949104091</v>
       </c>
       <c r="K29">
         <v>10000000</v>
@@ -2326,47 +2294,47 @@
         <v>50</v>
       </c>
       <c r="N29">
-        <v>5261.0187360659693</v>
+        <v>4685.88392030768</v>
       </c>
       <c r="O29" s="3">
-        <f t="shared" si="0"/>
-        <v>1.187641198060799</v>
+        <f>IF(B29=0, 0, H29/B29)</f>
+        <v>0</v>
       </c>
       <c r="P29" s="4">
-        <f t="shared" si="1"/>
-        <v>11188.794554673868</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I29=0, 0, H29/I29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
       <c r="B30">
-        <v>521863.98364015803</v>
+        <v>418101.4395081357</v>
       </c>
       <c r="C30">
-        <v>395341.13021032081</v>
+        <v>515914.1362484914</v>
       </c>
       <c r="D30">
         <v>10000000</v>
       </c>
       <c r="E30">
-        <v>221788.19247423889</v>
+        <v>213191.7193939735</v>
       </c>
       <c r="F30">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
       <c r="H30">
-        <v>552279.91995565384</v>
+        <v>475324.688570276</v>
       </c>
       <c r="I30">
         <v>50</v>
       </c>
       <c r="J30">
-        <v>11319.07216689139</v>
+        <v>8149.306845514524</v>
       </c>
       <c r="K30">
         <v>10000000</v>
@@ -2378,47 +2346,47 @@
         <v>50</v>
       </c>
       <c r="N30">
-        <v>4440.1309206062142</v>
+        <v>5176.053223874062</v>
       </c>
       <c r="O30" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0582832639710744</v>
+        <f>IF(B30=0, 0, H30/B30)</f>
+        <v>0</v>
       </c>
       <c r="P30" s="4">
-        <f t="shared" si="1"/>
-        <v>11045.598399113076</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <f>IF(I30=0, 0, H30/I30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
       <c r="B31">
-        <v>491088.66780710028</v>
+        <v>508313.5485757562</v>
       </c>
       <c r="C31">
-        <v>479067.49332270247</v>
+        <v>411467.6224612897</v>
       </c>
       <c r="D31">
         <v>10000000</v>
       </c>
       <c r="E31">
-        <v>191853.56342008011</v>
+        <v>183603.6175853384</v>
       </c>
       <c r="F31">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G31">
         <v>50</v>
       </c>
       <c r="H31">
-        <v>478037.04481148161</v>
+        <v>384199.0308265872</v>
       </c>
       <c r="I31">
         <v>50</v>
       </c>
       <c r="J31">
-        <v>13159.835530736969</v>
+        <v>9069.265345033004</v>
       </c>
       <c r="K31">
         <v>10000000</v>
@@ -2430,15 +2398,15 @@
         <v>50</v>
       </c>
       <c r="N31">
-        <v>4972.4012147598778</v>
+        <v>5622.024741229629</v>
       </c>
       <c r="O31" s="3">
-        <f t="shared" si="0"/>
-        <v>0.9734230825282546</v>
+        <f>IF(B31=0, 0, H31/B31)</f>
+        <v>0</v>
       </c>
       <c r="P31" s="4">
-        <f t="shared" si="1"/>
-        <v>9560.7408962296322</v>
+        <f>IF(I31=0, 0, H31/I31)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2447,11 +2415,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2477,58 +2445,58 @@
         <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>50</v>
       </c>
       <c r="F2">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
-        <f t="shared" ref="I2:I31" si="0">IF(C2=0, 0, B2/C2)</f>
-        <v>0.9</v>
+        <f>IF(C2=0, 0, B2/C2)</f>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <f t="shared" ref="J2:J31" si="1">IF(C2=0, 0, H2/C2)</f>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C2=0, 0, H2/C2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>50</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -2540,188 +2508,188 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C3=0, 0, B3/C3)</f>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C3=0, 0, H3/C3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>50</v>
       </c>
       <c r="D4">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>50</v>
       </c>
       <c r="F4">
-        <v>213</v>
+        <v>156</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" si="0"/>
-        <v>1.02</v>
+        <f>IF(C4=0, 0, B4/C4)</f>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C4=0, 0, H4/C4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>50</v>
       </c>
       <c r="D5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>50</v>
       </c>
       <c r="F5">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="0"/>
-        <v>1.02</v>
+        <f>IF(C5=0, 0, B5/C5)</f>
+        <v>0</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C5=0, 0, H5/C5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>50</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6">
         <v>50</v>
       </c>
       <c r="F6">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="0"/>
-        <v>1.02</v>
+        <f>IF(C6=0, 0, B6/C6)</f>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C6=0, 0, H6/C6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>50</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>50</v>
       </c>
       <c r="F7">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C7=0, 0, B7/C7)</f>
+        <v>0</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C7=0, 0, H7/C7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
       <c r="D8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>50</v>
       </c>
       <c r="F8">
-        <v>161</v>
+        <v>306</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
+        <f>IF(C8=0, 0, B8/C8)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C8=0, 0, H8/C8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
@@ -2732,137 +2700,137 @@
         <v>50</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E9">
         <v>50</v>
       </c>
       <c r="F9">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
+        <f>IF(C9=0, 0, B9/C9)</f>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C9=0, 0, H9/C9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>50</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E10">
         <v>50</v>
       </c>
       <c r="F10">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
         <v>2</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
+        <f>IF(C10=0, 0, B10/C10)</f>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C10=0, 0, H10/C10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
       <c r="B11">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>50</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>50</v>
       </c>
       <c r="F11">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C11=0, 0, B11/C11)</f>
+        <v>0</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C11=0, 0, H11/C11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>50</v>
       </c>
       <c r="D12">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E12">
         <v>50</v>
       </c>
       <c r="F12">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C12=0, 0, B12/C12)</f>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C12=0, 0, H12/C12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -2874,7 +2842,7 @@
         <v>50</v>
       </c>
       <c r="F13">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2883,32 +2851,32 @@
         <v>0</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C13=0, 0, B13/C13)</f>
+        <v>0</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C13=0, 0, H13/C13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
       <c r="B14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14">
         <v>50</v>
       </c>
       <c r="D14">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E14">
         <v>50</v>
       </c>
       <c r="F14">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -2917,230 +2885,230 @@
         <v>1</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(C14=0, 0, B14/C14)</f>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C14=0, 0, H14/C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15">
         <v>50</v>
       </c>
       <c r="D15">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15">
         <v>50</v>
       </c>
       <c r="F15">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C15=0, 0, B15/C15)</f>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C15=0, 0, H15/C15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <v>50</v>
       </c>
       <c r="D16">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>50</v>
       </c>
       <c r="F16">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C16=0, 0, B16/C16)</f>
+        <v>0</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C16=0, 0, H16/C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>50</v>
       </c>
       <c r="D17">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E17">
         <v>50</v>
       </c>
       <c r="F17">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C17=0, 0, B17/C17)</f>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C17=0, 0, H17/C17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18">
         <v>50</v>
       </c>
       <c r="D18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>50</v>
       </c>
       <c r="F18">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C18=0, 0, B18/C18)</f>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C18=0, 0, H18/C18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>50</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E19">
         <v>50</v>
       </c>
       <c r="F19">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(C19=0, 0, B19/C19)</f>
+        <v>0</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C19=0, 0, H19/C19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>50</v>
       </c>
       <c r="D20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20">
         <v>50</v>
       </c>
       <c r="F20">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
         <v>1</v>
       </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <f t="shared" si="0"/>
-        <v>0.86</v>
+        <f>IF(C20=0, 0, B20/C20)</f>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C20=0, 0, H20/C20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>50</v>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E21">
         <v>50</v>
@@ -3149,242 +3117,242 @@
         <v>197</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" si="0"/>
-        <v>0.88</v>
+        <f>IF(C21=0, 0, B21/C21)</f>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C21=0, 0, H21/C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
       <c r="B22">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22">
         <v>50</v>
       </c>
       <c r="D22">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22">
         <v>50</v>
       </c>
       <c r="F22">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C22=0, 0, B22/C22)</f>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C22=0, 0, H22/C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
       <c r="B23">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>50</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E23">
         <v>50</v>
       </c>
       <c r="F23">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(C23=0, 0, B23/C23)</f>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C23=0, 0, H23/C23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
       <c r="B24">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>50</v>
       </c>
       <c r="D24">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E24">
         <v>50</v>
       </c>
       <c r="F24">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C24=0, 0, B24/C24)</f>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C24=0, 0, H24/C24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
       <c r="B25">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E25">
         <v>50</v>
       </c>
       <c r="F25">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C25=0, 0, B25/C25)</f>
+        <v>0</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C25=0, 0, H25/C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
       <c r="B26">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>50</v>
       </c>
       <c r="D26">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E26">
         <v>50</v>
       </c>
       <c r="F26">
-        <v>159</v>
+        <v>237</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C26=0, 0, B26/C26)</f>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C26=0, 0, H26/C26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
       <c r="B27">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>50</v>
       </c>
       <c r="D27">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E27">
         <v>50</v>
       </c>
       <c r="F27">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(C27=0, 0, B27/C27)</f>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C27=0, 0, H27/C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
       <c r="B28">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>50</v>
       </c>
       <c r="D28">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="F28">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -3393,83 +3361,83 @@
         <v>0</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="0"/>
-        <v>1.04</v>
+        <f>IF(C28=0, 0, B28/C28)</f>
+        <v>0</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C28=0, 0, H28/C28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
       <c r="B29">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>50</v>
       </c>
       <c r="D29">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29">
         <v>50</v>
       </c>
       <c r="F29">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(C29=0, 0, B29/C29)</f>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C29=0, 0, H29/C29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
       <c r="B30">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C30">
         <v>50</v>
       </c>
       <c r="D30">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30">
         <v>50</v>
       </c>
       <c r="F30">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(C30=0, 0, B30/C30)</f>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <f>IF(C30=0, 0, H30/C30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
@@ -3480,27 +3448,27 @@
         <v>50</v>
       </c>
       <c r="D31">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
       <c r="F31">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(C31=0, 0, B31/C31)</f>
+        <v>0</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" si="1"/>
-        <v>0.02</v>
+        <f>IF(C31=0, 0, H31/C31)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3509,11 +3477,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3539,24 +3507,24 @@
         <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2">
-        <v>132263.2489283027</v>
+        <v>146391.1399441192</v>
       </c>
       <c r="C2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2">
         <v>50</v>
@@ -3565,36 +3533,36 @@
         <v>50</v>
       </c>
       <c r="F2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G2">
         <v>100000</v>
       </c>
       <c r="H2">
-        <v>143670.00884465859</v>
+        <v>111225.4176251615</v>
       </c>
       <c r="I2" s="3">
-        <f t="shared" ref="I2:I31" si="0">IF(D2=0, 0, C2/D2)</f>
-        <v>0.94</v>
+        <f>IF(D2=0, 0, C2/D2)</f>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <f t="shared" ref="J2:J31" si="1">IF(G2=0, 0, (H2-G2)/G2)</f>
-        <v>0.43670008844658587</v>
+        <f>IF(G2=0, 0, (H2-G2)/G2)</f>
+        <v>0</v>
       </c>
       <c r="K2" s="4">
-        <f t="shared" ref="K2:K31" si="2">E2+F2</f>
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E2+F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3">
-        <v>134052.68400326429</v>
+        <v>151011.5761365639</v>
       </c>
       <c r="C3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -3603,36 +3571,36 @@
         <v>50</v>
       </c>
       <c r="F3">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G3">
         <v>100000</v>
       </c>
       <c r="H3">
-        <v>136424.53511415081</v>
+        <v>156642.6046907666</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D3=0, 0, C3/D3)</f>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" si="1"/>
-        <v>0.36424535114150813</v>
+        <f>IF(G3=0, 0, (H3-G3)/G3)</f>
+        <v>0</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E3+F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4">
-        <v>124229.2434876284</v>
+        <v>145348.9551065743</v>
       </c>
       <c r="C4">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -3641,36 +3609,36 @@
         <v>50</v>
       </c>
       <c r="F4">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G4">
         <v>100000</v>
       </c>
       <c r="H4">
-        <v>116856.02074219831</v>
+        <v>125973.8425835718</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(D4=0, 0, C4/D4)</f>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.16856020742198308</v>
+        <f>IF(G4=0, 0, (H4-G4)/G4)</f>
+        <v>0</v>
       </c>
       <c r="K4" s="4">
-        <f t="shared" si="2"/>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E4+F4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5">
-        <v>148603.67635537311</v>
+        <v>159582.1928007665</v>
       </c>
       <c r="C5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5">
         <v>50</v>
@@ -3679,33 +3647,33 @@
         <v>50</v>
       </c>
       <c r="F5">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G5">
         <v>100000</v>
       </c>
       <c r="H5">
-        <v>131417.79418061179</v>
+        <v>125783.4551976133</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D5=0, 0, C5/D5)</f>
+        <v>0</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" si="1"/>
-        <v>0.31417794180611791</v>
+        <f>IF(G5=0, 0, (H5-G5)/G5)</f>
+        <v>0</v>
       </c>
       <c r="K5" s="4">
-        <f t="shared" si="2"/>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E5+F5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6">
-        <v>145535.41574162501</v>
+        <v>125164.4968283967</v>
       </c>
       <c r="C6">
         <v>49</v>
@@ -3717,36 +3685,36 @@
         <v>50</v>
       </c>
       <c r="F6">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G6">
         <v>100000</v>
       </c>
       <c r="H6">
-        <v>167562.9214711517</v>
+        <v>139659.8103828497</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(D6=0, 0, C6/D6)</f>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.67562921471151693</v>
+        <f>IF(G6=0, 0, (H6-G6)/G6)</f>
+        <v>0</v>
       </c>
       <c r="K6" s="4">
-        <f t="shared" si="2"/>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E6+F6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7">
-        <v>159899.20607369181</v>
+        <v>151144.5977361465</v>
       </c>
       <c r="C7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -3755,36 +3723,36 @@
         <v>50</v>
       </c>
       <c r="F7">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G7">
         <v>100000</v>
       </c>
       <c r="H7">
-        <v>159240.71094856161</v>
+        <v>128857.6365800039</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
+        <f>IF(D7=0, 0, C7/D7)</f>
+        <v>0</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="1"/>
-        <v>0.59240710948561615</v>
+        <f>IF(G7=0, 0, (H7-G7)/G7)</f>
+        <v>0</v>
       </c>
       <c r="K7" s="4">
-        <f t="shared" si="2"/>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E7+F7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8">
-        <v>148292.5357211286</v>
+        <v>130873.6165716724</v>
       </c>
       <c r="C8">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -3793,36 +3761,36 @@
         <v>50</v>
       </c>
       <c r="F8">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G8">
         <v>100000</v>
       </c>
       <c r="H8">
-        <v>146838.153167935</v>
+        <v>143530.6186089719</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
+        <f>IF(D8=0, 0, C8/D8)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="1"/>
-        <v>0.46838153167934998</v>
+        <f>IF(G8=0, 0, (H8-G8)/G8)</f>
+        <v>0</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E8+F8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
       <c r="B9">
-        <v>112913.444310823</v>
+        <v>181482.6630435414</v>
       </c>
       <c r="C9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9">
         <v>50</v>
@@ -3831,36 +3799,36 @@
         <v>50</v>
       </c>
       <c r="F9">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9">
         <v>100000</v>
       </c>
       <c r="H9">
-        <v>137730.10361687239</v>
+        <v>158395.2027942082</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D9=0, 0, C9/D9)</f>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="1"/>
-        <v>0.37730103616872396</v>
+        <f>IF(G9=0, 0, (H9-G9)/G9)</f>
+        <v>0</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="2"/>
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E9+F9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10">
-        <v>193688.4955264767</v>
+        <v>134890.8884906571</v>
       </c>
       <c r="C10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -3869,33 +3837,33 @@
         <v>50</v>
       </c>
       <c r="F10">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G10">
         <v>100000</v>
       </c>
       <c r="H10">
-        <v>126163.0375634644</v>
+        <v>113513.7553570183</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D10=0, 0, C10/D10)</f>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="1"/>
-        <v>0.26163037563464403</v>
+        <f>IF(G10=0, 0, (H10-G10)/G10)</f>
+        <v>0</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E10+F10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
       <c r="B11">
-        <v>166566.90438824211</v>
+        <v>157668.3101600282</v>
       </c>
       <c r="C11">
         <v>48</v>
@@ -3907,36 +3875,36 @@
         <v>50</v>
       </c>
       <c r="F11">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11">
         <v>100000</v>
       </c>
       <c r="H11">
-        <v>136165.34822166161</v>
+        <v>123742.8476439269</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D11=0, 0, C11/D11)</f>
+        <v>0</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="1"/>
-        <v>0.36165348221661608</v>
+        <f>IF(G11=0, 0, (H11-G11)/G11)</f>
+        <v>0</v>
       </c>
       <c r="K11" s="4">
-        <f t="shared" si="2"/>
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E11+F11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12">
-        <v>142861.60477608399</v>
+        <v>151288.7898635463</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12">
         <v>50</v>
@@ -3945,33 +3913,33 @@
         <v>50</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12">
         <v>100000</v>
       </c>
       <c r="H12">
-        <v>141062.6399765707</v>
+        <v>136949.4381191816</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(D12=0, 0, C12/D12)</f>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="1"/>
-        <v>0.41062639976570703</v>
+        <f>IF(G12=0, 0, (H12-G12)/G12)</f>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E12+F12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13">
-        <v>150172.33955955741</v>
+        <v>134186.5615931207</v>
       </c>
       <c r="C13">
         <v>49</v>
@@ -3983,36 +3951,36 @@
         <v>50</v>
       </c>
       <c r="F13">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G13">
         <v>100000</v>
       </c>
       <c r="H13">
-        <v>124640.6522217952</v>
+        <v>132598.1394564541</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(D13=0, 0, C13/D13)</f>
+        <v>0</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="1"/>
-        <v>0.24640652221795201</v>
+        <f>IF(G13=0, 0, (H13-G13)/G13)</f>
+        <v>0</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" si="2"/>
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E13+F13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
       <c r="B14">
-        <v>164246.82317952081</v>
+        <v>179033.2718417775</v>
       </c>
       <c r="C14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14">
         <v>50</v>
@@ -4021,36 +3989,36 @@
         <v>50</v>
       </c>
       <c r="F14">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14">
         <v>100000</v>
       </c>
       <c r="H14">
-        <v>143446.1741930297</v>
+        <v>103387.1420001699</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D14=0, 0, C14/D14)</f>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="1"/>
-        <v>0.43446174193029702</v>
+        <f>IF(G14=0, 0, (H14-G14)/G14)</f>
+        <v>0</v>
       </c>
       <c r="K14" s="4">
-        <f t="shared" si="2"/>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E14+F14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15">
-        <v>129548.7548336055</v>
+        <v>145841.2840669089</v>
       </c>
       <c r="C15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <v>50</v>
@@ -4059,36 +4027,36 @@
         <v>50</v>
       </c>
       <c r="F15">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G15">
         <v>100000</v>
       </c>
       <c r="H15">
-        <v>164937.2925505577</v>
+        <v>153454.8789297133</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D15=0, 0, C15/D15)</f>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="1"/>
-        <v>0.64937292550557701</v>
+        <f>IF(G15=0, 0, (H15-G15)/G15)</f>
+        <v>0</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" si="2"/>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E15+F15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16">
-        <v>182212.87233627931</v>
+        <v>148974.5224435105</v>
       </c>
       <c r="C16">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16">
         <v>50</v>
@@ -4103,30 +4071,30 @@
         <v>100000</v>
       </c>
       <c r="H16">
-        <v>138978.26925868631</v>
+        <v>116982.4895604343</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D16=0, 0, C16/D16)</f>
+        <v>0</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="1"/>
-        <v>0.3897826925868631</v>
+        <f>IF(G16=0, 0, (H16-G16)/G16)</f>
+        <v>0</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="2"/>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E16+F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17">
-        <v>110518.78252879879</v>
+        <v>185534.3338870773</v>
       </c>
       <c r="C17">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17">
         <v>50</v>
@@ -4135,36 +4103,36 @@
         <v>50</v>
       </c>
       <c r="F17">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G17">
         <v>100000</v>
       </c>
       <c r="H17">
-        <v>136513.50549477289</v>
+        <v>140114.1813472628</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D17=0, 0, C17/D17)</f>
+        <v>0</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="1"/>
-        <v>0.36513505494772891</v>
+        <f>IF(G17=0, 0, (H17-G17)/G17)</f>
+        <v>0</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="2"/>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E17+F17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18">
-        <v>144239.08110537651</v>
+        <v>165020.6503666715</v>
       </c>
       <c r="C18">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <v>50</v>
@@ -4179,30 +4147,30 @@
         <v>100000</v>
       </c>
       <c r="H18">
-        <v>118947.8542451652</v>
+        <v>145375.5269311373</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="0"/>
-        <v>1.06</v>
+        <f>IF(D18=0, 0, C18/D18)</f>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="1"/>
-        <v>0.18947854245165202</v>
+        <f>IF(G18=0, 0, (H18-G18)/G18)</f>
+        <v>0</v>
       </c>
       <c r="K18" s="4">
-        <f t="shared" si="2"/>
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E18+F18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19">
-        <v>166873.15810359741</v>
+        <v>149844.1772444801</v>
       </c>
       <c r="C19">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D19">
         <v>50</v>
@@ -4211,36 +4179,36 @@
         <v>50</v>
       </c>
       <c r="F19">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G19">
         <v>100000</v>
       </c>
       <c r="H19">
-        <v>143627.70267610039</v>
+        <v>135516.5980517882</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="0"/>
-        <v>1.06</v>
+        <f>IF(D19=0, 0, C19/D19)</f>
+        <v>0</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="1"/>
-        <v>0.43627702676100394</v>
+        <f>IF(G19=0, 0, (H19-G19)/G19)</f>
+        <v>0</v>
       </c>
       <c r="K19" s="4">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E19+F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20">
-        <v>143172.44858066851</v>
+        <v>117270.4246670839</v>
       </c>
       <c r="C20">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D20">
         <v>50</v>
@@ -4249,36 +4217,36 @@
         <v>50</v>
       </c>
       <c r="F20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100000</v>
       </c>
       <c r="H20">
-        <v>131380.82968471269</v>
+        <v>142599.0914925668</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(D20=0, 0, C20/D20)</f>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="1"/>
-        <v>0.31380829684712691</v>
+        <f>IF(G20=0, 0, (H20-G20)/G20)</f>
+        <v>0</v>
       </c>
       <c r="K20" s="4">
-        <f t="shared" si="2"/>
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E20+F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21">
-        <v>186113.51856916741</v>
+        <v>164593.1465775182</v>
       </c>
       <c r="C21">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D21">
         <v>50</v>
@@ -4287,36 +4255,36 @@
         <v>50</v>
       </c>
       <c r="F21">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G21">
         <v>100000</v>
       </c>
       <c r="H21">
-        <v>116004.7877227499</v>
+        <v>141863.3185662146</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
+        <f>IF(D21=0, 0, C21/D21)</f>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="1"/>
-        <v>0.16004787722749897</v>
+        <f>IF(G21=0, 0, (H21-G21)/G21)</f>
+        <v>0</v>
       </c>
       <c r="K21" s="4">
-        <f t="shared" si="2"/>
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E21+F21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
       <c r="B22">
-        <v>170304.48912451751</v>
+        <v>142376.1081456944</v>
       </c>
       <c r="C22">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D22">
         <v>50</v>
@@ -4325,33 +4293,33 @@
         <v>50</v>
       </c>
       <c r="F22">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="G22">
         <v>100000</v>
       </c>
       <c r="H22">
-        <v>148755.87384367461</v>
+        <v>139898.126417628</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(D22=0, 0, C22/D22)</f>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="1"/>
-        <v>0.48755873843674608</v>
+        <f>IF(G22=0, 0, (H22-G22)/G22)</f>
+        <v>0</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" si="2"/>
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E22+F22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
       <c r="B23">
-        <v>123551.04620045979</v>
+        <v>130116.4877166419</v>
       </c>
       <c r="C23">
         <v>48</v>
@@ -4369,30 +4337,30 @@
         <v>100000</v>
       </c>
       <c r="H23">
-        <v>141797.52421018641</v>
+        <v>153335.3742636866</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D23=0, 0, C23/D23)</f>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="1"/>
-        <v>0.41797524210186415</v>
+        <f>IF(G23=0, 0, (H23-G23)/G23)</f>
+        <v>0</v>
       </c>
       <c r="K23" s="4">
-        <f t="shared" si="2"/>
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E23+F23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
       <c r="B24">
-        <v>150281.18075329269</v>
+        <v>162240.7614919289</v>
       </c>
       <c r="C24">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D24">
         <v>50</v>
@@ -4401,36 +4369,36 @@
         <v>50</v>
       </c>
       <c r="F24">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G24">
         <v>100000</v>
       </c>
       <c r="H24">
-        <v>134839.19135426599</v>
+        <v>149162.8581940508</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(D24=0, 0, C24/D24)</f>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" si="1"/>
-        <v>0.34839191354265991</v>
+        <f>IF(G24=0, 0, (H24-G24)/G24)</f>
+        <v>0</v>
       </c>
       <c r="K24" s="4">
-        <f t="shared" si="2"/>
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E24+F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
       <c r="B25">
-        <v>129842.492109382</v>
+        <v>190678.8358967547</v>
       </c>
       <c r="C25">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D25">
         <v>50</v>
@@ -4439,36 +4407,36 @@
         <v>50</v>
       </c>
       <c r="F25">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G25">
         <v>100000</v>
       </c>
       <c r="H25">
-        <v>147667.9151390187</v>
+        <v>123058.1078543188</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(D25=0, 0, C25/D25)</f>
+        <v>0</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="1"/>
-        <v>0.47667915139018702</v>
+        <f>IF(G25=0, 0, (H25-G25)/G25)</f>
+        <v>0</v>
       </c>
       <c r="K25" s="4">
-        <f t="shared" si="2"/>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E25+F25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
       <c r="B26">
-        <v>157719.74875475219</v>
+        <v>149469.3011621555</v>
       </c>
       <c r="C26">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D26">
         <v>50</v>
@@ -4477,36 +4445,36 @@
         <v>50</v>
       </c>
       <c r="F26">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G26">
         <v>100000</v>
       </c>
       <c r="H26">
-        <v>139655.46570326429</v>
+        <v>131457.5674441383</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
+        <f>IF(D26=0, 0, C26/D26)</f>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.39655465703264287</v>
+        <f>IF(G26=0, 0, (H26-G26)/G26)</f>
+        <v>0</v>
       </c>
       <c r="K26" s="4">
-        <f t="shared" si="2"/>
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E26+F26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
       <c r="B27">
-        <v>176295.77676212639</v>
+        <v>134050.0745410774</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>50</v>
@@ -4515,36 +4483,36 @@
         <v>50</v>
       </c>
       <c r="F27">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G27">
         <v>100000</v>
       </c>
       <c r="H27">
-        <v>139022.2394406478</v>
+        <v>133714.1014258281</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98</v>
+        <f>IF(D27=0, 0, C27/D27)</f>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="1"/>
-        <v>0.39022239440647799</v>
+        <f>IF(G27=0, 0, (H27-G27)/G27)</f>
+        <v>0</v>
       </c>
       <c r="K27" s="4">
-        <f t="shared" si="2"/>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E27+F27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
       <c r="B28">
-        <v>179021.5809457094</v>
+        <v>169142.8994998968</v>
       </c>
       <c r="C28">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D28">
         <v>50</v>
@@ -4553,36 +4521,36 @@
         <v>50</v>
       </c>
       <c r="F28">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G28">
         <v>100000</v>
       </c>
       <c r="H28">
-        <v>137765.59504157171</v>
+        <v>167415.2076852944</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D28=0, 0, C28/D28)</f>
+        <v>0</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" si="1"/>
-        <v>0.37765595041571709</v>
+        <f>IF(G28=0, 0, (H28-G28)/G28)</f>
+        <v>0</v>
       </c>
       <c r="K28" s="4">
-        <f t="shared" si="2"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E28+F28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
       <c r="B29">
-        <v>152739.49783500671</v>
+        <v>108527.1945340192</v>
       </c>
       <c r="C29">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D29">
         <v>50</v>
@@ -4591,36 +4559,36 @@
         <v>50</v>
       </c>
       <c r="F29">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100000</v>
       </c>
       <c r="H29">
-        <v>134176.3419571394</v>
+        <v>154363.1959301738</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
+        <f>IF(D29=0, 0, C29/D29)</f>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="1"/>
-        <v>0.34176341957139406</v>
+        <f>IF(G29=0, 0, (H29-G29)/G29)</f>
+        <v>0</v>
       </c>
       <c r="K29" s="4">
-        <f t="shared" si="2"/>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E29+F29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
       <c r="B30">
-        <v>124461.99812589549</v>
+        <v>136794.9214546526</v>
       </c>
       <c r="C30">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D30">
         <v>50</v>
@@ -4629,36 +4597,36 @@
         <v>50</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G30">
         <v>100000</v>
       </c>
       <c r="H30">
-        <v>140225.39507007651</v>
+        <v>131601.487843231</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
+        <f>IF(D30=0, 0, C30/D30)</f>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="1"/>
-        <v>0.40225395070076514</v>
+        <f>IF(G30=0, 0, (H30-G30)/G30)</f>
+        <v>0</v>
       </c>
       <c r="K30" s="4">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <f>E30+F30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
       <c r="B31">
-        <v>183976.02739053429</v>
+        <v>154324.1212355525</v>
       </c>
       <c r="C31">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D31">
         <v>50</v>
@@ -4673,19 +4641,19 @@
         <v>100000</v>
       </c>
       <c r="H31">
-        <v>136631.85101871891</v>
+        <v>136883.1138176506</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
+        <f>IF(D31=0, 0, C31/D31)</f>
+        <v>0</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" si="1"/>
-        <v>0.36631851018718908</v>
+        <f>IF(G31=0, 0, (H31-G31)/G31)</f>
+        <v>0</v>
       </c>
       <c r="K31" s="4">
-        <f t="shared" si="2"/>
-        <v>154</v>
+        <f>E31+F31</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4694,11 +4662,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4721,253 +4689,253 @@
         <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>374636.80845510197</v>
+        <v>358319.1531611675</v>
       </c>
       <c r="E2">
-        <v>3520.6911788742732</v>
+        <v>3798.355595528516</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H2" s="3">
-        <f t="shared" ref="H2:H31" si="0">IF(C2=0, 0, B2/C2)</f>
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C2=0, 0, B2/C2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>50</v>
       </c>
       <c r="D3">
-        <v>369466.67961571761</v>
+        <v>451941.1249496234</v>
       </c>
       <c r="E3">
-        <v>3475.0768113651998</v>
+        <v>3989.543602721239</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C3=0, 0, B3/C3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>50</v>
       </c>
       <c r="D4">
-        <v>381954.47680985811</v>
+        <v>352555.0839696701</v>
       </c>
       <c r="E4">
-        <v>3869.5895449873051</v>
+        <v>4423.715845110752</v>
       </c>
       <c r="F4">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C4=0, 0, B4/C4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>50</v>
       </c>
       <c r="D5">
-        <v>491998.41453119548</v>
+        <v>417908.6381177033</v>
       </c>
       <c r="E5">
-        <v>4276.5422406129319</v>
+        <v>4001.733860297565</v>
       </c>
       <c r="F5">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="H5" s="3">
-        <f t="shared" si="0"/>
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C5=0, 0, B5/C5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>50</v>
       </c>
       <c r="D6">
-        <v>434530.71724952862</v>
+        <v>466925.8731198857</v>
       </c>
       <c r="E6">
-        <v>3702.1871722255928</v>
+        <v>4894.57072860644</v>
       </c>
       <c r="F6">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="0"/>
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C6=0, 0, B6/C6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>50</v>
       </c>
       <c r="D7">
-        <v>341553.92773478088</v>
+        <v>412272.5868462806</v>
       </c>
       <c r="E7">
-        <v>3565.3789576679842</v>
+        <v>4050.35031680021</v>
       </c>
       <c r="F7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G7">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C7=0, 0, B7/C7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
       <c r="D8">
-        <v>424508.93925768201</v>
+        <v>378209.2129367004</v>
       </c>
       <c r="E8">
-        <v>2927.2287402552088</v>
+        <v>4627.626485541565</v>
       </c>
       <c r="F8">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="0"/>
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C8=0, 0, B8/C8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
       <c r="B9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>50</v>
       </c>
       <c r="D9">
-        <v>383572.80752067512</v>
+        <v>392715.7176744071</v>
       </c>
       <c r="E9">
-        <v>3417.1733910703442</v>
+        <v>4270.100634586407</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G9">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C9=0, 0, B9/C9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>50</v>
       </c>
       <c r="D10">
-        <v>397679.21407528158</v>
+        <v>507941.7006006223</v>
       </c>
       <c r="E10">
-        <v>4349.7137472982085</v>
+        <v>3983.515183288589</v>
       </c>
       <c r="F10">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G10">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="0"/>
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C10=0, 0, B10/C10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
@@ -4978,77 +4946,77 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>340589.89915768302</v>
+        <v>419349.0380812833</v>
       </c>
       <c r="E11">
-        <v>3459.4617942318778</v>
+        <v>4311.630513069645</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C11=0, 0, B11/C11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>50</v>
       </c>
       <c r="D12">
-        <v>422654.97582123609</v>
+        <v>330805.5182556851</v>
       </c>
       <c r="E12">
-        <v>4178.1230218433984</v>
+        <v>3856.735875164137</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G12">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C12=0, 0, B12/C12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>50</v>
       </c>
       <c r="D13">
-        <v>412507.35535119142</v>
+        <v>382836.9140407501</v>
       </c>
       <c r="E13">
-        <v>3931.2540852047609</v>
+        <v>3475.214363215143</v>
       </c>
       <c r="F13">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" si="0"/>
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C13=0, 0, B13/C13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
@@ -5059,239 +5027,239 @@
         <v>50</v>
       </c>
       <c r="D14">
-        <v>377555.18245776149</v>
+        <v>480970.4443176017</v>
       </c>
       <c r="E14">
-        <v>4399.1213029355613</v>
+        <v>3918.170762150903</v>
       </c>
       <c r="F14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C14=0, 0, B14/C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>50</v>
       </c>
       <c r="D15">
-        <v>390477.19770340592</v>
+        <v>412528.5124244988</v>
       </c>
       <c r="E15">
-        <v>3863.416383323814</v>
+        <v>3951.17916417273</v>
       </c>
       <c r="F15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G15">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="0"/>
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C15=0, 0, B15/C15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16">
         <v>50</v>
       </c>
       <c r="D16">
-        <v>411159.76575752237</v>
+        <v>431927.9672423804</v>
       </c>
       <c r="E16">
-        <v>3777.032502521562</v>
+        <v>5335.338156174624</v>
       </c>
       <c r="F16">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G16">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H16" s="3">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C16=0, 0, B16/C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <v>50</v>
       </c>
       <c r="D17">
-        <v>380531.2324403915</v>
+        <v>415706.8176567859</v>
       </c>
       <c r="E17">
-        <v>3548.040551270507</v>
+        <v>3996.19609195887</v>
       </c>
       <c r="F17">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G17">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" si="0"/>
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C17=0, 0, B17/C17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>50</v>
       </c>
       <c r="D18">
-        <v>462993.74251106707</v>
+        <v>299433.4337620742</v>
       </c>
       <c r="E18">
-        <v>4214.0776716894043</v>
+        <v>4090.401835893488</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G18">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C18=0, 0, B18/C18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>50</v>
       </c>
       <c r="D19">
-        <v>338955.47519713279</v>
+        <v>377824.7411786407</v>
       </c>
       <c r="E19">
-        <v>3571.7788995992642</v>
+        <v>4510.793980329403</v>
       </c>
       <c r="F19">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="0"/>
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C19=0, 0, B19/C19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>50</v>
       </c>
       <c r="D20">
-        <v>374932.04040478269</v>
+        <v>356996.4377379033</v>
       </c>
       <c r="E20">
-        <v>4254.4519334258994</v>
+        <v>3489.137637232147</v>
       </c>
       <c r="F20">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G20">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="0"/>
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C20=0, 0, B20/C20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>50</v>
       </c>
       <c r="D21">
-        <v>355752.04405196162</v>
+        <v>353774.6914857876</v>
       </c>
       <c r="E21">
-        <v>2944.8230129221529</v>
+        <v>3915.186477272293</v>
       </c>
       <c r="F21">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G21">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3">
-        <f t="shared" si="0"/>
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C21=0, 0, B21/C21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
       <c r="B22">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>50</v>
       </c>
       <c r="D22">
-        <v>432326.62216962402</v>
+        <v>440065.3762815904</v>
       </c>
       <c r="E22">
-        <v>4735.970696286282</v>
+        <v>3223.066548291979</v>
       </c>
       <c r="F22">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G22">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H22" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C22=0, 0, B22/C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
@@ -5302,236 +5270,236 @@
         <v>50</v>
       </c>
       <c r="D23">
-        <v>451151.91868506791</v>
+        <v>364692.2418339433</v>
       </c>
       <c r="E23">
-        <v>3487.8390125810029</v>
+        <v>3930.922646753571</v>
       </c>
       <c r="F23">
         <v>45</v>
       </c>
       <c r="G23">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C23=0, 0, B23/C23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
       <c r="B24">
+        <v>38</v>
+      </c>
+      <c r="C24">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>461158.199225402</v>
+      </c>
+      <c r="E24">
+        <v>4414.901944387911</v>
+      </c>
+      <c r="F24">
         <v>40</v>
       </c>
-      <c r="C24">
-        <v>50</v>
-      </c>
-      <c r="D24">
-        <v>451781.40056480502</v>
-      </c>
-      <c r="E24">
-        <v>4655.7864382211374</v>
-      </c>
-      <c r="F24">
-        <v>45</v>
-      </c>
       <c r="G24">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C24=0, 0, B24/C24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
       <c r="B25">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25">
-        <v>449112.05612071691</v>
+        <v>420664.177834098</v>
       </c>
       <c r="E25">
-        <v>4779.3135613377453</v>
+        <v>4050.597559217126</v>
       </c>
       <c r="F25">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G25">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C25=0, 0, B25/C25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
       <c r="B26">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C26">
         <v>50</v>
       </c>
       <c r="D26">
-        <v>520475.82615522167</v>
+        <v>419086.5505132863</v>
       </c>
       <c r="E26">
-        <v>4031.2654187253952</v>
+        <v>3241.726568403089</v>
       </c>
       <c r="F26">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G26">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C26=0, 0, B26/C26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
       <c r="B27">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>50</v>
       </c>
       <c r="D27">
-        <v>376327.2307645625</v>
+        <v>391773.7486854541</v>
       </c>
       <c r="E27">
-        <v>4236.3821347834601</v>
+        <v>4374.059641176342</v>
       </c>
       <c r="F27">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G27">
         <v>44</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="0"/>
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C27=0, 0, B27/C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
       <c r="B28">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>50</v>
       </c>
       <c r="D28">
-        <v>345196.38543344382</v>
+        <v>384505.6796605996</v>
       </c>
       <c r="E28">
-        <v>4491.213587271397</v>
+        <v>3691.732422489635</v>
       </c>
       <c r="F28">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G28">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C28=0, 0, B28/C28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
       <c r="B29">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>50</v>
       </c>
       <c r="D29">
-        <v>342163.38266736938</v>
+        <v>402996.8904349711</v>
       </c>
       <c r="E29">
-        <v>4108.0084581418714</v>
+        <v>4629.026462030094</v>
       </c>
       <c r="F29">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G29">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C29=0, 0, B29/C29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
       <c r="B30">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>50</v>
       </c>
       <c r="D30">
-        <v>390030.72888981813</v>
+        <v>368000.4332488994</v>
       </c>
       <c r="E30">
-        <v>3244.5488210419908</v>
+        <v>4852.064988987911</v>
       </c>
       <c r="F30">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G30">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IF(C30=0, 0, B30/C30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
       <c r="B31">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>50</v>
       </c>
       <c r="D31">
-        <v>450437.145383442</v>
+        <v>339617.3875609907</v>
       </c>
       <c r="E31">
-        <v>3473.3010346927522</v>
+        <v>3365.032848716099</v>
       </c>
       <c r="F31">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G31">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="0"/>
-        <v>0.82</v>
+        <f>IF(C31=0, 0, B31/C31)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5540,256 +5508,844 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2">
-        <v>87.7907781082383</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2" s="3">
+        <f>IF(OR(C2=0,E2=0,G2=0),0,((B2/C2)*0.4+(D2/E2)*0.3+(1-F2/G2)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3">
-        <v>79.027984005235311</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3">
+        <f>IF(OR(C3=0,E3=0,G3=0),0,((B3/C3)*0.4+(D3/E3)*0.3+(1-F3/G3)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4">
-        <v>83.799634031792763</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>38</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3">
+        <f>IF(OR(C4=0,E4=0,G4=0),0,((B4/C4)*0.4+(D4/E4)*0.3+(1-F4/G4)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5">
-        <v>83.826428738269669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>49</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5" s="3">
+        <f>IF(OR(C5=0,E5=0,G5=0),0,((B5/C5)*0.4+(D5/E5)*0.3+(1-F5/G5)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6">
-        <v>84.720809680470694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>43</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6" s="3">
+        <f>IF(OR(C6=0,E6=0,G6=0),0,((B6/C6)*0.4+(D6/E6)*0.3+(1-F6/G6)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7">
-        <v>77.196289547739468</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7" s="3">
+        <f>IF(OR(C7=0,E7=0,G7=0),0,((B7/C7)*0.4+(D7/E7)*0.3+(1-F7/G7)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8">
-        <v>84.548834740104851</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>48</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3">
+        <f>IF(OR(C8=0,E8=0,G8=0),0,((B8/C8)*0.4+(D8/E8)*0.3+(1-F8/G8)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
       <c r="B9">
-        <v>86.829965624971805</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9" s="3">
+        <f>IF(OR(C9=0,E9=0,G9=0),0,((B9/C9)*0.4+(D9/E9)*0.3+(1-F9/G9)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10">
-        <v>79.62455924500189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+      <c r="H10" s="3">
+        <f>IF(OR(C10=0,E10=0,G10=0),0,((B10/C10)*0.4+(D10/E10)*0.3+(1-F10/G10)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
       <c r="B11">
-        <v>93.721284530620963</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>47</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11" s="3">
+        <f>IF(OR(C11=0,E11=0,G11=0),0,((B11/C11)*0.4+(D11/E11)*0.3+(1-F11/G11)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12">
-        <v>88.866204172025363</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="C12">
+        <v>50</v>
+      </c>
+      <c r="D12">
+        <v>51</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>50</v>
+      </c>
+      <c r="H12" s="3">
+        <f>IF(OR(C12=0,E12=0,G12=0),0,((B12/C12)*0.4+(D12/E12)*0.3+(1-F12/G12)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13">
-        <v>87.364491640482058</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="C13">
+        <v>50</v>
+      </c>
+      <c r="D13">
+        <v>45</v>
+      </c>
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13" s="3">
+        <f>IF(OR(C13=0,E13=0,G13=0),0,((B13/C13)*0.4+(D13/E13)*0.3+(1-F13/G13)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
       <c r="B14">
-        <v>84.841187081176386</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C14">
+        <v>50</v>
+      </c>
+      <c r="D14">
+        <v>45</v>
+      </c>
+      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14" s="3">
+        <f>IF(OR(C14=0,E14=0,G14=0),0,((B14/C14)*0.4+(D14/E14)*0.3+(1-F14/G14)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15">
-        <v>85.961034190387764</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="C15">
+        <v>50</v>
+      </c>
+      <c r="D15">
+        <v>43</v>
+      </c>
+      <c r="E15">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>50</v>
+      </c>
+      <c r="H15" s="3">
+        <f>IF(OR(C15=0,E15=0,G15=0),0,((B15/C15)*0.4+(D15/E15)*0.3+(1-F15/G15)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16">
-        <v>82.137913465961958</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>50</v>
+      </c>
+      <c r="H16" s="3">
+        <f>IF(OR(C16=0,E16=0,G16=0),0,((B16/C16)*0.4+(D16/E16)*0.3+(1-F16/G16)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17">
-        <v>84.26146754880503</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="C17">
+        <v>50</v>
+      </c>
+      <c r="D17">
+        <v>44</v>
+      </c>
+      <c r="E17">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17" s="3">
+        <f>IF(OR(C17=0,E17=0,G17=0),0,((B17/C17)*0.4+(D17/E17)*0.3+(1-F17/G17)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18">
-        <v>89.205700366335194</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>50</v>
+      </c>
+      <c r="H18" s="3">
+        <f>IF(OR(C18=0,E18=0,G18=0),0,((B18/C18)*0.4+(D18/E18)*0.3+(1-F18/G18)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19">
-        <v>81.84013493774026</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C19">
+        <v>50</v>
+      </c>
+      <c r="D19">
+        <v>46</v>
+      </c>
+      <c r="E19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19" s="3">
+        <f>IF(OR(C19=0,E19=0,G19=0),0,((B19/C19)*0.4+(D19/E19)*0.3+(1-F19/G19)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20">
-        <v>88.449420360921835</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>44</v>
+      </c>
+      <c r="E20">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20" s="3">
+        <f>IF(OR(C20=0,E20=0,G20=0),0,((B20/C20)*0.4+(D20/E20)*0.3+(1-F20/G20)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21">
-        <v>81.654957786169675</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="C21">
+        <v>50</v>
+      </c>
+      <c r="D21">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>50</v>
+      </c>
+      <c r="H21" s="3">
+        <f>IF(OR(C21=0,E21=0,G21=0),0,((B21/C21)*0.4+(D21/E21)*0.3+(1-F21/G21)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
       <c r="B22">
-        <v>88.01325497653977</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>50</v>
+      </c>
+      <c r="D22">
+        <v>46</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="H22" s="3">
+        <f>IF(OR(C22=0,E22=0,G22=0),0,((B22/C22)*0.4+(D22/E22)*0.3+(1-F22/G22)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
       <c r="B23">
-        <v>93.399301315955185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="C23">
+        <v>50</v>
+      </c>
+      <c r="D23">
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <v>50</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>50</v>
+      </c>
+      <c r="H23" s="3">
+        <f>IF(OR(C23=0,E23=0,G23=0),0,((B23/C23)*0.4+(D23/E23)*0.3+(1-F23/G23)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
       <c r="B24">
-        <v>87.429710760852899</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="C24">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+      <c r="E24">
+        <v>50</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>50</v>
+      </c>
+      <c r="H24" s="3">
+        <f>IF(OR(C24=0,E24=0,G24=0),0,((B24/C24)*0.4+(D24/E24)*0.3+(1-F24/G24)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
       <c r="B25">
-        <v>81.160692670096438</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>44</v>
+      </c>
+      <c r="E25">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>50</v>
+      </c>
+      <c r="H25" s="3">
+        <f>IF(OR(C25=0,E25=0,G25=0),0,((B25/C25)*0.4+(D25/E25)*0.3+(1-F25/G25)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
       <c r="B26">
-        <v>95.29651270308095</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>45</v>
+      </c>
+      <c r="E26">
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>50</v>
+      </c>
+      <c r="H26" s="3">
+        <f>IF(OR(C26=0,E26=0,G26=0),0,((B26/C26)*0.4+(D26/E26)*0.3+(1-F26/G26)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
       <c r="B27">
-        <v>81.865728851382997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="C27">
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>50</v>
+      </c>
+      <c r="H27" s="3">
+        <f>IF(OR(C27=0,E27=0,G27=0),0,((B27/C27)*0.4+(D27/E27)*0.3+(1-F27/G27)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
       <c r="B28">
-        <v>91.071900684124884</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>50</v>
+      </c>
+      <c r="D28">
+        <v>55</v>
+      </c>
+      <c r="E28">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>50</v>
+      </c>
+      <c r="H28" s="3">
+        <f>IF(OR(C28=0,E28=0,G28=0),0,((B28/C28)*0.4+(D28/E28)*0.3+(1-F28/G28)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
       <c r="B29">
-        <v>76.322160362674126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C29">
+        <v>50</v>
+      </c>
+      <c r="D29">
+        <v>54</v>
+      </c>
+      <c r="E29">
+        <v>50</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>50</v>
+      </c>
+      <c r="H29" s="3">
+        <f>IF(OR(C29=0,E29=0,G29=0),0,((B29/C29)*0.4+(D29/E29)*0.3+(1-F29/G29)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
       <c r="B30">
-        <v>86.092226684755104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="C30">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>53</v>
+      </c>
+      <c r="E30">
+        <v>50</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>50</v>
+      </c>
+      <c r="H30" s="3">
+        <f>IF(OR(C30=0,E30=0,G30=0),0,((B30/C30)*0.4+(D30/E30)*0.3+(1-F30/G30)*0.2)/0.9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
       <c r="B31">
-        <v>79.035440436842649</v>
+        <v>49</v>
+      </c>
+      <c r="C31">
+        <v>50</v>
+      </c>
+      <c r="D31">
+        <v>45</v>
+      </c>
+      <c r="E31">
+        <v>50</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>50</v>
+      </c>
+      <c r="H31" s="3">
+        <f>IF(OR(C31=0,E31=0,G31=0),0,((B31/C31)*0.4+(D31/E31)*0.3+(1-F31/G31)*0.2)/0.9)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5798,161 +6354,161 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="2">
         <v>45403</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" s="2">
         <v>45404</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" s="2">
         <v>45405</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" s="2">
         <v>45406</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" s="2">
         <v>45407</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" s="2">
         <v>45408</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" s="2">
         <v>45409</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" s="2">
         <v>45410</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" s="2">
         <v>45411</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" s="2">
         <v>45412</v>
       </c>
@@ -5963,436 +6519,428 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>45383</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>45384</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
         <v>45385</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
         <v>45386</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
         <v>45387</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
         <v>45388</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
         <v>45389</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
         <v>45390</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
         <v>45391</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
         <v>45392</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
         <v>45393</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
         <v>45394</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2">
         <v>45395</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
         <v>45396</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
         <v>45397</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2">
         <v>45398</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2">
         <v>45399</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2">
         <v>45400</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2">
         <v>45401</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2">
         <v>45402</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
